--- a/artfynd/A 27581-2025 artfynd.xlsx
+++ b/artfynd/A 27581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,6 +1504,134 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129866902</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mårdbergets barrskogar, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>539219</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6436696</v>
+      </c>
+      <c r="S8" t="n">
+        <v>46</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västra Eneby</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>E-Kin-0759</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sammanslagning av 3 lokaler. Avverkningsanmält: A 11477-2025</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27581-2025 artfynd.xlsx
+++ b/artfynd/A 27581-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2025 artfynd.xlsx
+++ b/artfynd/A 27581-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2025 artfynd.xlsx
+++ b/artfynd/A 27581-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2025 artfynd.xlsx
+++ b/artfynd/A 27581-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2025 artfynd.xlsx
+++ b/artfynd/A 27581-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2025 artfynd.xlsx
+++ b/artfynd/A 27581-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2025 artfynd.xlsx
+++ b/artfynd/A 27581-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2025 artfynd.xlsx
+++ b/artfynd/A 27581-2025 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>129866902</v>
       </c>
       <c r="B8" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2025 artfynd.xlsx
+++ b/artfynd/A 27581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123580093</v>
+        <v>123580152</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -735,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539222</v>
+        <v>539296</v>
       </c>
       <c r="R2" t="n">
-        <v>6436675</v>
+        <v>6436714</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -783,20 +763,29 @@
           <t>13:13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Avverkningsanmält: A 11477-2025</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>ekar</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -813,57 +802,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123580939</v>
+        <v>123580522</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -872,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539227</v>
+        <v>539273</v>
       </c>
       <c r="R3" t="n">
-        <v>6436728</v>
+        <v>6436711</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -917,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Avverkningsanmält: A 11477-2025</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -949,63 +914,63 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123580880</v>
+        <v>123579996</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mårdbergets barrskogar, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539211</v>
+        <v>539176</v>
       </c>
       <c r="R4" t="n">
-        <v>6436801</v>
+        <v>6436662</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält: A 11477-2025</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,6 +1023,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1079,59 +1050,45 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>William Rosén, Amanda Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123579966</v>
+        <v>123580824</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1145,13 +1102,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539176</v>
+        <v>539225</v>
       </c>
       <c r="R5" t="n">
-        <v>6436662</v>
+        <v>6436842</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1180,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1190,12 +1147,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Avverkningsanmält: A 11477-2025</t>
+          <t>En individ hördes dessutom</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1222,54 +1179,35 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123581028</v>
+        <v>123582733</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>101675</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Geoffroy, 1785)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1281,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539308</v>
+        <v>539265</v>
       </c>
       <c r="R6" t="n">
-        <v>6436591</v>
+        <v>6436720</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1316,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1326,12 +1264,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Avverkningsanmält: A 11477-2025</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1342,6 +1280,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1358,68 +1311,58 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123579996</v>
+        <v>123580880</v>
       </c>
       <c r="B7" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mårdbergets barrskogar, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539176</v>
+        <v>539211</v>
       </c>
       <c r="R7" t="n">
-        <v>6436662</v>
+        <v>6436801</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1448,7 +1391,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1458,12 +1401,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Avverkningsanmält: A 11477-2025</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1472,7 +1410,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1499,17 +1436,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Rosén, Amanda Olsson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129866902</v>
+        <v>123579966</v>
       </c>
       <c r="B8" t="n">
-        <v>98833</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1473,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1549,21 +1486,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mårdbergets barrskogar, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539219</v>
+        <v>539176</v>
       </c>
       <c r="R8" t="n">
-        <v>6436696</v>
+        <v>6436662</v>
       </c>
       <c r="S8" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1585,24 +1525,29 @@
           <t>Västra Eneby</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>E-Kin-0759</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-29</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Sammanslagning av 3 lokaler. Avverkningsanmält: A 11477-2025</t>
+          <t>Avverkningsanmält: A 11477-2025</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1611,22 +1556,671 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>William Rosén, Amanda Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123580093</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mårdbergets barrskogar, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>539222</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6436675</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västra Eneby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält: A 11477-2025</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123580682</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mårdbergets barrskogar, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>539217</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6436816</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Västra Eneby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält: A 11477-2025</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123580939</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mårdbergets barrskogar, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>539227</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6436728</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Västra Eneby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält: A 11477-2025</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123581028</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mårdbergets barrskogar, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>539308</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6436591</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Västra Eneby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Avverkningsanmält: A 11477-2025</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129866902</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mårdbergets barrskogar, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>539219</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6436696</v>
+      </c>
+      <c r="S13" t="n">
+        <v>46</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Västra Eneby</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>E-Kin-0759</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Sammanslagning av 3 lokaler. Avverkningsanmält: A 11477-2025</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Karin Nyström</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>William Rosén</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 27581-2025 artfynd.xlsx
+++ b/artfynd/A 27581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580152</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580522</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1054,6 +1069,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123579996</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580824</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1308,6 +1333,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123582733</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1440,6 +1470,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580880</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1571,6 +1606,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123579966</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1704,6 +1744,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580093</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1835,6 +1880,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580682</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1966,6 +2016,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580939</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2097,6 +2152,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123581028</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2225,8 +2285,27 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129866902</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>